--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
   </si>
   <si>
     <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>VALERY MIRANDA</t>
@@ -581,19 +572,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>23</v>
       </c>
       <c r="G3">
-        <v>58.97</v>
+        <v>60.53</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -607,7 +598,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -616,10 +607,10 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H4">
         <v>6.7</v>
@@ -659,10 +650,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -671,7 +662,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -747,13 +738,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -770,13 +761,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -816,10 +807,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -904,19 +895,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>23</v>
       </c>
       <c r="G3">
-        <v>58.97</v>
+        <v>60.53</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -930,7 +921,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -939,10 +930,10 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H4">
         <v>6.7</v>
@@ -982,10 +973,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -994,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -1007,7 +998,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1045,10 +1036,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1062,16 +1053,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920213</v>
+        <v>23330051920242</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1085,16 +1076,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920242</v>
+        <v>23330051920257</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1108,16 +1099,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920257</v>
+        <v>23330051920275</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1131,22 +1122,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920275</v>
+        <v>23330051920222</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1154,39 +1145,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920222</v>
+        <v>23330051920181</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920181</v>
+        <v>23330051920185</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1200,16 +1191,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920185</v>
+        <v>23330051920203</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1218,29 +1209,6 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920203</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,42 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -94,19 +127,43 @@
     <t>CUAPIO</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
   </si>
   <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
   </si>
   <si>
     <t>ALVAREZ</t>
@@ -118,18 +175,45 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
   </si>
   <si>
     <t>NATANAHEL</t>
   </si>
   <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>VALERY MIRANDA</t>
   </si>
   <si>
@@ -142,13 +226,10 @@
     <t>JESSICA</t>
   </si>
   <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -572,19 +653,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>23</v>
       </c>
       <c r="G3">
-        <v>60.53</v>
+        <v>58.97</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -653,16 +734,16 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>63.16</v>
+        <v>68.42</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -718,16 +799,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>36.11</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -738,13 +822,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -810,16 +894,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>63.16</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -875,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>36.11</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -895,19 +982,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>23</v>
       </c>
       <c r="G3">
-        <v>60.53</v>
+        <v>58.97</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -976,10 +1063,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -988,7 +1075,7 @@
         <v>63.16</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1030,16 +1117,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920189</v>
+        <v>23330051920180</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1053,22 +1140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920242</v>
+        <v>23330051920181</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1076,22 +1163,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920257</v>
+        <v>23330051920189</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1099,22 +1186,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920275</v>
+        <v>23330051920203</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1122,22 +1209,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920222</v>
+        <v>23330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1145,70 +1232,300 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920181</v>
+        <v>23330051920260</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920185</v>
+        <v>23330051920229</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920203</v>
+        <v>23330051920299</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920300</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920332</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920329</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920213</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920242</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920257</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920275</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920222</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920292</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920295</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -94,7 +94,10 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>MORENO</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -103,81 +106,42 @@
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
     <t>JOSE EMILIANO</t>
   </si>
   <si>
@@ -193,7 +157,10 @@
     <t>ALEX URIEL</t>
   </si>
   <si>
-    <t>FATIMA</t>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
   </si>
   <si>
     <t>MARIANA</t>
@@ -202,34 +169,10 @@
     <t>MICHEL LEONEL</t>
   </si>
   <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
     <t>SABDY</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
     <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -825,16 +768,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,16 +794,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>61.54</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,16 +820,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>40.54</v>
+      </c>
+      <c r="H5">
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -988,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>58.97</v>
+        <v>56.41</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1014,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>64.09999999999999</v>
+        <v>61.54</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1040,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>54.05</v>
+        <v>40.54</v>
       </c>
       <c r="H5">
         <v>5.9</v>
@@ -1085,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,10 +1098,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1169,10 +1121,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1192,10 +1144,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1215,10 +1167,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1232,16 +1184,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920260</v>
+        <v>23330051920275</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1255,16 +1207,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920229</v>
+        <v>23330051920222</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1278,7 +1230,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920299</v>
+        <v>23330051920229</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1287,13 +1239,13 @@
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1301,22 +1253,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920300</v>
+        <v>23330051920299</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1324,208 +1276,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920332</v>
+        <v>23330051920329</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920329</v>
+        <v>23330051920242</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920213</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920242</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920257</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920275</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920222</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920292</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920295</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,102 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
   </si>
 </sst>
 </file>
@@ -914,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>36.11</v>
+        <v>72.22</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -940,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>56.41</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -966,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>61.54</v>
+        <v>76.92</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -992,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>40.54</v>
+        <v>48.65</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1018,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>63.16</v>
+        <v>78.95</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1067,259 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920180</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920181</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920189</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920203</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920212</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920275</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920222</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920229</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920299</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920329</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920242</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>LUCIA</t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920347</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -836,7 +836,7 @@
         <v>72.22</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -862,7 +862,7 @@
         <v>84.62</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -888,7 +888,7 @@
         <v>76.92</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -914,7 +914,7 @@
         <v>48.65</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -940,7 +940,7 @@
         <v>78.95</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20231.xlsx
@@ -836,7 +836,7 @@
         <v>72.22</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -862,7 +862,7 @@
         <v>84.62</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -888,7 +888,7 @@
         <v>76.92</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -914,7 +914,7 @@
         <v>48.65</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -940,7 +940,7 @@
         <v>78.95</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
